--- a/output/yearly_benthic_cover_iteration_51_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_51_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.18998608498175</v>
+        <v>45.47026835314402</v>
       </c>
       <c r="M2" t="n">
-        <v>100.1842301264587</v>
+        <v>99.91838274125899</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.91523709066485</v>
+        <v>88.00994629169354</v>
       </c>
       <c r="C3" t="n">
-        <v>45.86370228368234</v>
+        <v>45.92070691871404</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228492130923537</v>
+        <v>2.228692119038064</v>
       </c>
       <c r="E3" t="n">
-        <v>5.663157780552824</v>
+        <v>5.700838929564291</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742830710307846</v>
+        <v>0.742897373012688</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95172755913494</v>
+        <v>33.97053724938274</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17021267416091</v>
+        <v>34.17327915858364</v>
       </c>
       <c r="I3" t="n">
-        <v>6.516124296160752</v>
+        <v>6.550592880782813</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642691939424036</v>
+        <v>4.643108581329299</v>
       </c>
       <c r="K3" t="n">
-        <v>12.08476290933515</v>
+        <v>11.99005370830646</v>
       </c>
       <c r="L3" t="n">
-        <v>48.81761432933791</v>
+        <v>48.85410261901242</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7660795223554</v>
+        <v>106.7648632460329</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.94969947961097</v>
+        <v>87.10218948962438</v>
       </c>
       <c r="C4" t="n">
-        <v>42.52568783322094</v>
+        <v>42.64501343570403</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181611052079001</v>
+        <v>2.184972458082157</v>
       </c>
       <c r="E4" t="n">
-        <v>6.450926364244696</v>
+        <v>6.500716261163934</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443802890092952</v>
+        <v>0.7444525723803915</v>
       </c>
       <c r="G4" t="n">
-        <v>33.23748064997114</v>
+        <v>33.30414624887342</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24149329442757</v>
+        <v>34.244818329498</v>
       </c>
       <c r="I4" t="n">
-        <v>5.441431023571176</v>
+        <v>5.470255042249016</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652376806308094</v>
+        <v>4.652828577377447</v>
       </c>
       <c r="K4" t="n">
-        <v>13.05030052038903</v>
+        <v>12.8978105103756</v>
       </c>
       <c r="L4" t="n">
-        <v>44.24300819371891</v>
+        <v>44.27521514056529</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81899654732888</v>
+        <v>99.81803908664493</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.68034984525951</v>
+        <v>85.89541312184247</v>
       </c>
       <c r="C5" t="n">
-        <v>42.10080302978199</v>
+        <v>42.28726881747478</v>
       </c>
       <c r="D5" t="n">
-        <v>2.11921093821945</v>
+        <v>2.125937794387821</v>
       </c>
       <c r="E5" t="n">
-        <v>7.023501927007138</v>
+        <v>7.086180762864889</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7456957897213619</v>
+        <v>0.7457718648897388</v>
       </c>
       <c r="G5" t="n">
-        <v>32.28679671619368</v>
+        <v>32.4043183969677</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30200632718264</v>
+        <v>34.30550578492797</v>
       </c>
       <c r="I5" t="n">
-        <v>4.54253946117672</v>
+        <v>4.566624362243477</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660598685758511</v>
+        <v>4.661074155560867</v>
       </c>
       <c r="K5" t="n">
-        <v>14.3196501547405</v>
+        <v>14.10458687815754</v>
       </c>
       <c r="L5" t="n">
-        <v>43.42839595371164</v>
+        <v>43.4561927754163</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84884913823414</v>
+        <v>99.8480484710486</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.04704910080211</v>
+        <v>84.43096397408485</v>
       </c>
       <c r="C6" t="n">
-        <v>41.172812885181</v>
+        <v>41.53201305499746</v>
       </c>
       <c r="D6" t="n">
-        <v>2.038724778550567</v>
+        <v>2.054214032907531</v>
       </c>
       <c r="E6" t="n">
-        <v>7.388611080439189</v>
+        <v>7.482318687314008</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468170022311035</v>
+        <v>0.7468940125768038</v>
       </c>
       <c r="G6" t="n">
-        <v>31.06056659967698</v>
+        <v>31.31107869363728</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35358210263075</v>
+        <v>34.35712457853296</v>
       </c>
       <c r="I6" t="n">
-        <v>3.791141273329122</v>
+        <v>3.811246390511233</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667606263944395</v>
+        <v>4.668087578605022</v>
       </c>
       <c r="K6" t="n">
-        <v>15.9529508991979</v>
+        <v>15.56903602591515</v>
       </c>
       <c r="L6" t="n">
-        <v>42.74805456392175</v>
+        <v>42.77210024235841</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87381834830065</v>
+        <v>99.87314932327102</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.13595686992959</v>
+        <v>82.68393689453801</v>
       </c>
       <c r="C7" t="n">
-        <v>39.8501746290988</v>
+        <v>40.37681812334868</v>
       </c>
       <c r="D7" t="n">
-        <v>1.944987523703933</v>
+        <v>1.968877506553182</v>
       </c>
       <c r="E7" t="n">
-        <v>7.576118111769153</v>
+        <v>7.70150527609486</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477757525582551</v>
+        <v>0.7478515566674691</v>
       </c>
       <c r="G7" t="n">
-        <v>29.63245218341686</v>
+        <v>30.01034826860909</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39768461767973</v>
+        <v>34.40117160670356</v>
       </c>
       <c r="I7" t="n">
-        <v>3.163340227312557</v>
+        <v>3.180110450738155</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673598453489093</v>
+        <v>4.674072229171681</v>
       </c>
       <c r="K7" t="n">
-        <v>17.86404313007043</v>
+        <v>17.31606310546199</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18047276101608</v>
+        <v>42.20125081589735</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89469052018532</v>
+        <v>99.89413204470802</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86.96746082957098</v>
+        <v>87.51066367448026</v>
       </c>
       <c r="C8" t="n">
-        <v>42.19887584112827</v>
+        <v>42.71990983574693</v>
       </c>
       <c r="D8" t="n">
-        <v>1.949106471749983</v>
+        <v>1.973034381609269</v>
       </c>
       <c r="E8" t="n">
-        <v>9.434056025977322</v>
+        <v>9.556476247106445</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493593357110242</v>
+        <v>0.749430489572751</v>
       </c>
       <c r="G8" t="n">
-        <v>30.15571960776347</v>
+        <v>30.53116291542326</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4705294427071</v>
+        <v>34.47380252034654</v>
       </c>
       <c r="I8" t="n">
-        <v>5.525194097468173</v>
+        <v>5.542816560592299</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6834958481939</v>
+        <v>4.683940559829693</v>
       </c>
       <c r="K8" t="n">
-        <v>13.03253917042902</v>
+        <v>12.48933632551974</v>
       </c>
       <c r="L8" t="n">
-        <v>44.58480105562744</v>
+        <v>44.60638254831854</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81621606718473</v>
+        <v>99.81562870958521</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.58680787172266</v>
+        <v>85.1514538983669</v>
       </c>
       <c r="C9" t="n">
-        <v>40.67497655244627</v>
+        <v>41.22072989101396</v>
       </c>
       <c r="D9" t="n">
-        <v>1.840740293341996</v>
+        <v>1.865739183313027</v>
       </c>
       <c r="E9" t="n">
-        <v>9.678325535231023</v>
+        <v>9.808017512166449</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507214741270536</v>
+        <v>0.7507880315838247</v>
       </c>
       <c r="G9" t="n">
-        <v>28.47912567182415</v>
+        <v>28.87085369336434</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53318780984446</v>
+        <v>34.53624945285593</v>
       </c>
       <c r="I9" t="n">
-        <v>4.612697874059885</v>
+        <v>4.627380827684421</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692009213294083</v>
+        <v>4.692425197398904</v>
       </c>
       <c r="K9" t="n">
-        <v>15.41319212827735</v>
+        <v>14.8485461016331</v>
       </c>
       <c r="L9" t="n">
-        <v>43.75835370545781</v>
+        <v>43.77675688066982</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84652238618143</v>
+        <v>99.84603287331689</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.06537477577119</v>
+        <v>82.50911787359493</v>
       </c>
       <c r="C10" t="n">
-        <v>38.86813236108109</v>
+        <v>39.2957541772785</v>
       </c>
       <c r="D10" t="n">
-        <v>1.727399486838077</v>
+        <v>1.746868337941788</v>
       </c>
       <c r="E10" t="n">
-        <v>9.724051553409542</v>
+        <v>9.826819097294347</v>
       </c>
       <c r="F10" t="n">
-        <v>0.751895425192414</v>
+        <v>0.7519594855854043</v>
       </c>
       <c r="G10" t="n">
-        <v>26.72556647401324</v>
+        <v>27.0314203921751</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58718955885104</v>
+        <v>34.59013633692859</v>
       </c>
       <c r="I10" t="n">
-        <v>3.849925870014282</v>
+        <v>3.862167438760916</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699346407452587</v>
+        <v>4.699746784908776</v>
       </c>
       <c r="K10" t="n">
-        <v>17.93462522422881</v>
+        <v>17.49088212640508</v>
       </c>
       <c r="L10" t="n">
-        <v>43.06911191818845</v>
+        <v>43.08482533999185</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87186950349835</v>
+        <v>99.87146164367543</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.40063109136534</v>
+        <v>79.6330634559631</v>
       </c>
       <c r="C11" t="n">
-        <v>36.79888118143831</v>
+        <v>37.01742503963717</v>
       </c>
       <c r="D11" t="n">
-        <v>1.608994659668189</v>
+        <v>1.618908838037652</v>
       </c>
       <c r="E11" t="n">
-        <v>9.592948234168524</v>
+        <v>9.644132534536592</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529094969497246</v>
+        <v>0.7529738992632311</v>
       </c>
       <c r="G11" t="n">
-        <v>24.89365897173347</v>
+        <v>25.05134727506966</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63383685968732</v>
+        <v>34.63679936610863</v>
       </c>
       <c r="I11" t="n">
-        <v>3.212598513222329</v>
+        <v>3.222814672552154</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705684355935777</v>
+        <v>4.706086870395193</v>
       </c>
       <c r="K11" t="n">
-        <v>20.59936890863464</v>
+        <v>20.3669365440369</v>
       </c>
       <c r="L11" t="n">
-        <v>42.49480752464886</v>
+        <v>42.50835598747146</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89305761472183</v>
+        <v>99.89271757114552</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>76.71628253272884</v>
+        <v>76.82051319334697</v>
       </c>
       <c r="C12" t="n">
-        <v>34.61035704183096</v>
+        <v>34.70242543325658</v>
       </c>
       <c r="D12" t="n">
-        <v>1.491071815873448</v>
+        <v>1.495266816272132</v>
       </c>
       <c r="E12" t="n">
-        <v>9.336597162636457</v>
+        <v>9.355710047612114</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537863254506788</v>
+        <v>0.7538523996335837</v>
       </c>
       <c r="G12" t="n">
-        <v>23.0692085046271</v>
+        <v>23.13808375320623</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67417097073121</v>
+        <v>34.67721038314485</v>
       </c>
       <c r="I12" t="n">
-        <v>2.680283219343201</v>
+        <v>2.688812295768158</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711164534066741</v>
+        <v>4.711577497709897</v>
       </c>
       <c r="K12" t="n">
-        <v>23.28371746727114</v>
+        <v>23.17948680665304</v>
       </c>
       <c r="L12" t="n">
-        <v>42.01668664330838</v>
+        <v>42.02856513029728</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91076115241049</v>
+        <v>99.91047737020691</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.10868201486325</v>
+        <v>74.23431430374434</v>
       </c>
       <c r="C13" t="n">
-        <v>32.41532484896419</v>
+        <v>32.53016027931147</v>
       </c>
       <c r="D13" t="n">
-        <v>1.377751595828722</v>
+        <v>1.382884587308023</v>
       </c>
       <c r="E13" t="n">
-        <v>8.999659451996301</v>
+        <v>9.026369815569881</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545443685159443</v>
+        <v>0.7546116356132265</v>
       </c>
       <c r="G13" t="n">
-        <v>21.31596781147467</v>
+        <v>21.39905671278383</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70904095173342</v>
+        <v>34.71213523820842</v>
       </c>
       <c r="I13" t="n">
-        <v>2.235815532089544</v>
+        <v>2.242933591678314</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715902303224651</v>
+        <v>4.716322722582665</v>
       </c>
       <c r="K13" t="n">
-        <v>25.89131798513675</v>
+        <v>25.76568569625564</v>
       </c>
       <c r="L13" t="n">
-        <v>41.61890485425062</v>
+        <v>41.62946479399487</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92554768835156</v>
+        <v>99.92531076956199</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>81.99109500265368</v>
+        <v>81.96029757717147</v>
       </c>
       <c r="C14" t="n">
-        <v>37.32620916831964</v>
+        <v>37.45085911494572</v>
       </c>
       <c r="D14" t="n">
-        <v>1.379404936184454</v>
+        <v>1.384447519979875</v>
       </c>
       <c r="E14" t="n">
-        <v>11.69850830841506</v>
+        <v>11.71488004835606</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554498428107553</v>
+        <v>0.7554644957800721</v>
       </c>
       <c r="G14" t="n">
-        <v>23.53763857335236</v>
+        <v>23.63839391732088</v>
       </c>
       <c r="H14" t="n">
-        <v>36.94678377506043</v>
+        <v>36.96651885050883</v>
       </c>
       <c r="I14" t="n">
-        <v>2.951748049263404</v>
+        <v>2.778939646600302</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72156151756722</v>
+        <v>4.721653098625449</v>
       </c>
       <c r="K14" t="n">
-        <v>18.0089049973463</v>
+        <v>18.03970242282852</v>
       </c>
       <c r="L14" t="n">
-        <v>44.56661216383849</v>
+        <v>44.41691171416964</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90172632950443</v>
+        <v>99.90747325194388</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.08869214786415</v>
+        <v>80.99085117165887</v>
       </c>
       <c r="C15" t="n">
-        <v>36.85608833537263</v>
+        <v>36.90970341572989</v>
       </c>
       <c r="D15" t="n">
-        <v>1.344228114171104</v>
+        <v>1.34920021799172</v>
       </c>
       <c r="E15" t="n">
-        <v>11.83305760758281</v>
+        <v>11.80295744998329</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562144906812157</v>
+        <v>0.7561852195327253</v>
       </c>
       <c r="G15" t="n">
-        <v>22.95989295492249</v>
+        <v>23.03657290432149</v>
       </c>
       <c r="H15" t="n">
-        <v>37.00667863332481</v>
+        <v>37.00178542933191</v>
       </c>
       <c r="I15" t="n">
-        <v>2.462279780424113</v>
+        <v>2.317992328418208</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726340566757597</v>
+        <v>4.726157622079532</v>
       </c>
       <c r="K15" t="n">
-        <v>18.91130785213588</v>
+        <v>19.00914882834112</v>
       </c>
       <c r="L15" t="n">
-        <v>44.15061081112304</v>
+        <v>44.00395498796787</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91800699863154</v>
+        <v>99.92280723203888</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.27798774051365</v>
+        <v>78.318052864324</v>
       </c>
       <c r="C16" t="n">
-        <v>34.42467206284385</v>
+        <v>34.5940608634413</v>
       </c>
       <c r="D16" t="n">
-        <v>1.240759872430912</v>
+        <v>1.250580224177097</v>
       </c>
       <c r="E16" t="n">
-        <v>11.26452309916212</v>
+        <v>11.26242677198757</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568758231996574</v>
+        <v>0.7568074238146862</v>
       </c>
       <c r="G16" t="n">
-        <v>21.19261868834183</v>
+        <v>21.35271112677452</v>
       </c>
       <c r="H16" t="n">
-        <v>37.03904209670898</v>
+        <v>37.03223123644324</v>
       </c>
       <c r="I16" t="n">
-        <v>2.053694265672298</v>
+        <v>1.933249682285093</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730473894997858</v>
+        <v>4.730046398841787</v>
       </c>
       <c r="K16" t="n">
-        <v>21.72201225948633</v>
+        <v>21.68194713567602</v>
       </c>
       <c r="L16" t="n">
-        <v>43.7849190171025</v>
+        <v>43.65960332509329</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9316033394327</v>
+        <v>99.93561132421061</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.27964368227138</v>
+        <v>80.28973604867103</v>
       </c>
       <c r="C17" t="n">
-        <v>35.85387592686471</v>
+        <v>36.02117867992275</v>
       </c>
       <c r="D17" t="n">
-        <v>1.241821895194981</v>
+        <v>1.251568542040342</v>
       </c>
       <c r="E17" t="n">
-        <v>12.14610040307515</v>
+        <v>12.12983649018979</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575236676147388</v>
+        <v>0.7574055192279451</v>
       </c>
       <c r="G17" t="n">
-        <v>21.7391189228495</v>
+        <v>21.9108352141072</v>
       </c>
       <c r="H17" t="n">
-        <v>37.59910600518992</v>
+        <v>37.60274665182661</v>
       </c>
       <c r="I17" t="n">
-        <v>2.061449865754975</v>
+        <v>1.903559136104483</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734522922592117</v>
+        <v>4.733784495174655</v>
       </c>
       <c r="K17" t="n">
-        <v>19.72035631772864</v>
+        <v>19.71026395132898</v>
       </c>
       <c r="L17" t="n">
-        <v>44.35711152586859</v>
+        <v>44.20515550324376</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93134377046192</v>
+        <v>99.93659813449548</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>77.55532325541759</v>
+        <v>77.81460282410914</v>
       </c>
       <c r="C18" t="n">
-        <v>33.44655694323546</v>
+        <v>33.83889575435128</v>
       </c>
       <c r="D18" t="n">
-        <v>1.146357292842269</v>
+        <v>1.164584263941075</v>
       </c>
       <c r="E18" t="n">
-        <v>11.49889742771999</v>
+        <v>11.5513732807751</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580833938293955</v>
+        <v>0.7579205420156686</v>
       </c>
       <c r="G18" t="n">
-        <v>20.06793213551854</v>
+        <v>20.38802753747444</v>
       </c>
       <c r="H18" t="n">
-        <v>37.62688758638464</v>
+        <v>37.62831587586188</v>
       </c>
       <c r="I18" t="n">
-        <v>1.719144207689041</v>
+        <v>1.587377936443081</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738021211433721</v>
+        <v>4.737003387597927</v>
       </c>
       <c r="K18" t="n">
-        <v>22.44467674458241</v>
+        <v>22.18539717589083</v>
       </c>
       <c r="L18" t="n">
-        <v>44.05150381591118</v>
+        <v>43.92283042708834</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94273750372903</v>
+        <v>99.94712335733045</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.47549895551653</v>
+        <v>76.88221739443188</v>
       </c>
       <c r="C19" t="n">
-        <v>32.60617297757783</v>
+        <v>33.1327771334513</v>
       </c>
       <c r="D19" t="n">
-        <v>1.10824221214377</v>
+        <v>1.131737406320554</v>
       </c>
       <c r="E19" t="n">
-        <v>11.35937412999837</v>
+        <v>11.44894423965234</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585647615181189</v>
+        <v>0.7583609573470416</v>
       </c>
       <c r="G19" t="n">
-        <v>19.400696137132</v>
+        <v>19.81298744941724</v>
       </c>
       <c r="H19" t="n">
-        <v>37.65077990226801</v>
+        <v>37.65018107978075</v>
       </c>
       <c r="I19" t="n">
-        <v>1.456812052968019</v>
+        <v>1.340250278494954</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741029759488242</v>
+        <v>4.739755983419007</v>
       </c>
       <c r="K19" t="n">
-        <v>23.52450104448348</v>
+        <v>23.11778260556811</v>
       </c>
       <c r="L19" t="n">
-        <v>43.82079639148321</v>
+        <v>43.70479119654443</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9514704135445</v>
+        <v>99.95535093556384</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>73.65931639597638</v>
+        <v>74.35584675718542</v>
       </c>
       <c r="C20" t="n">
-        <v>30.01302968860878</v>
+        <v>30.81180528750388</v>
       </c>
       <c r="D20" t="n">
-        <v>1.010862899315072</v>
+        <v>1.043996329569265</v>
       </c>
       <c r="E20" t="n">
-        <v>10.56369193851033</v>
+        <v>10.74757224977081</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589817313780519</v>
+        <v>0.75874085074737</v>
       </c>
       <c r="G20" t="n">
-        <v>17.69599075997642</v>
+        <v>18.2769307256906</v>
       </c>
       <c r="H20" t="n">
-        <v>37.67147588133089</v>
+        <v>37.66904156458658</v>
       </c>
       <c r="I20" t="n">
-        <v>1.214677364352794</v>
+        <v>1.117434719649719</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743635821112823</v>
+        <v>4.74213031717106</v>
       </c>
       <c r="K20" t="n">
-        <v>26.34068360402362</v>
+        <v>25.64415324281459</v>
       </c>
       <c r="L20" t="n">
-        <v>43.60581970589627</v>
+        <v>43.50681229527889</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95953299852867</v>
+        <v>99.96277082559736</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.38716469084048</v>
+        <v>80.92806840597228</v>
       </c>
       <c r="C21" t="n">
-        <v>34.26488676406671</v>
+        <v>35.01123502194444</v>
       </c>
       <c r="D21" t="n">
-        <v>1.011564708331788</v>
+        <v>1.044636605867195</v>
       </c>
       <c r="E21" t="n">
-        <v>12.82970135881927</v>
+        <v>12.97152578110429</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595086675461168</v>
+        <v>0.7592061816774176</v>
       </c>
       <c r="G21" t="n">
-        <v>19.68790101846398</v>
+        <v>20.25733862068817</v>
       </c>
       <c r="H21" t="n">
-        <v>39.67725446516795</v>
+        <v>39.66134251762018</v>
       </c>
       <c r="I21" t="n">
-        <v>1.674305300348143</v>
+        <v>1.488980063531173</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746929172163228</v>
+        <v>4.745038635483857</v>
       </c>
       <c r="K21" t="n">
-        <v>19.61283530915953</v>
+        <v>19.07193159402771</v>
       </c>
       <c r="L21" t="n">
-        <v>46.06650647039178</v>
+        <v>45.86723113598621</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94422854361801</v>
+        <v>99.95039775195836</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_51_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_51_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.47026835314402</v>
+        <v>45.25870206488339</v>
       </c>
       <c r="M2" t="n">
-        <v>99.91838274125899</v>
+        <v>100.5276397246814</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00994629169354</v>
+        <v>88.0441503817095</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92070691871404</v>
+        <v>45.92741034658017</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228692119038064</v>
+        <v>2.228774775912142</v>
       </c>
       <c r="E3" t="n">
-        <v>5.700838929564291</v>
+        <v>5.706573525980716</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742897373012688</v>
+        <v>0.7429249253040474</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97053724938274</v>
+        <v>33.97249914922985</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17327915858364</v>
+        <v>34.17454656398618</v>
       </c>
       <c r="I3" t="n">
-        <v>6.550592880782813</v>
+        <v>6.575550658146275</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643108581329299</v>
+        <v>4.643280783150296</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99005370830646</v>
+        <v>11.9558496182905</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85410261901242</v>
+        <v>48.88071616302837</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7648632460329</v>
+        <v>106.763976127899</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.10218948962438</v>
+        <v>87.18285183697407</v>
       </c>
       <c r="C4" t="n">
-        <v>42.64501343570403</v>
+        <v>42.70274475643387</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184972458082157</v>
+        <v>2.187551620546124</v>
       </c>
       <c r="E4" t="n">
-        <v>6.500716261163934</v>
+        <v>6.516213723539072</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444525723803915</v>
+        <v>0.7444846728721171</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30414624887342</v>
+        <v>33.34414781210228</v>
       </c>
       <c r="H4" t="n">
-        <v>34.244818329498</v>
+        <v>34.24629495211738</v>
       </c>
       <c r="I4" t="n">
-        <v>5.470255042249016</v>
+        <v>5.491129850346349</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652828577377447</v>
+        <v>4.65302920545073</v>
       </c>
       <c r="K4" t="n">
-        <v>12.8978105103756</v>
+        <v>12.81714816302593</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27521514056529</v>
+        <v>44.2974528955917</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81803908664493</v>
+        <v>99.81734581505151</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.89541312184247</v>
+        <v>85.96436838222711</v>
       </c>
       <c r="C5" t="n">
-        <v>42.28726881747478</v>
+        <v>42.33657129797183</v>
       </c>
       <c r="D5" t="n">
-        <v>2.125937794387821</v>
+        <v>2.12793547466299</v>
       </c>
       <c r="E5" t="n">
-        <v>7.086180762864889</v>
+        <v>7.102643474630181</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457718648897388</v>
+        <v>0.7458080017045735</v>
       </c>
       <c r="G5" t="n">
-        <v>32.4043183969677</v>
+        <v>32.43543801908773</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30550578492797</v>
+        <v>34.30716807841038</v>
       </c>
       <c r="I5" t="n">
-        <v>4.566624362243477</v>
+        <v>4.584075323077665</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661074155560867</v>
+        <v>4.661300010653583</v>
       </c>
       <c r="K5" t="n">
-        <v>14.10458687815754</v>
+        <v>14.03563161777291</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4561927754163</v>
+        <v>43.4752656995234</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8480484710486</v>
+        <v>99.84746861526813</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.43096397408485</v>
+        <v>84.6372952555857</v>
       </c>
       <c r="C6" t="n">
-        <v>41.53201305499746</v>
+        <v>41.72142897164933</v>
       </c>
       <c r="D6" t="n">
-        <v>2.054214032907531</v>
+        <v>2.063264341688932</v>
       </c>
       <c r="E6" t="n">
-        <v>7.482318687314008</v>
+        <v>7.524419987362557</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468940125768038</v>
+        <v>0.7469317482965094</v>
       </c>
       <c r="G6" t="n">
-        <v>31.31107869363728</v>
+        <v>31.44967667896231</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35712457853296</v>
+        <v>34.35886042163943</v>
       </c>
       <c r="I6" t="n">
-        <v>3.811246390511233</v>
+        <v>3.825818650782797</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668087578605022</v>
+        <v>4.668323426853182</v>
       </c>
       <c r="K6" t="n">
-        <v>15.56903602591515</v>
+        <v>15.36270474441428</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77210024235841</v>
+        <v>42.78853085829535</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87314932327102</v>
+        <v>99.87266457435896</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.68393689453801</v>
+        <v>83.06215224956689</v>
       </c>
       <c r="C7" t="n">
-        <v>40.37681812334868</v>
+        <v>40.7405134517891</v>
       </c>
       <c r="D7" t="n">
-        <v>1.968877506553182</v>
+        <v>1.986611508938463</v>
       </c>
       <c r="E7" t="n">
-        <v>7.70150527609486</v>
+        <v>7.776922858419468</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478515566674691</v>
+        <v>0.7478886242187196</v>
       </c>
       <c r="G7" t="n">
-        <v>30.01034826860909</v>
+        <v>30.28128213163276</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40117160670356</v>
+        <v>34.40287671406109</v>
       </c>
       <c r="I7" t="n">
-        <v>3.180110450738155</v>
+        <v>3.19226651092939</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674072229171681</v>
+        <v>4.674303901366995</v>
       </c>
       <c r="K7" t="n">
-        <v>17.31606310546199</v>
+        <v>16.9378477504331</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20125081589735</v>
+        <v>42.21536605747828</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89413204470802</v>
+        <v>99.89372725970048</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.51066367448026</v>
+        <v>87.9272910022987</v>
       </c>
       <c r="C8" t="n">
-        <v>42.71990983574693</v>
+        <v>43.02932077859809</v>
       </c>
       <c r="D8" t="n">
-        <v>1.973034381609269</v>
+        <v>1.99086296684368</v>
       </c>
       <c r="E8" t="n">
-        <v>9.556476247106445</v>
+        <v>9.601449390557452</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749430489572751</v>
+        <v>0.7494891470131113</v>
       </c>
       <c r="G8" t="n">
-        <v>30.53116291542326</v>
+        <v>30.77960438753249</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47380252034654</v>
+        <v>34.47650076260311</v>
       </c>
       <c r="I8" t="n">
-        <v>5.542816560592299</v>
+        <v>5.645077178916916</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683940559829693</v>
+        <v>4.684307168831944</v>
       </c>
       <c r="K8" t="n">
-        <v>12.48933632551974</v>
+        <v>12.0727089977013</v>
       </c>
       <c r="L8" t="n">
-        <v>44.60638254831854</v>
+        <v>44.71020281698214</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81562870958521</v>
+        <v>99.81223259328154</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.1514538983669</v>
+        <v>85.93327938075582</v>
       </c>
       <c r="C9" t="n">
-        <v>41.22072989101396</v>
+        <v>41.91143276747566</v>
       </c>
       <c r="D9" t="n">
-        <v>1.865739183313027</v>
+        <v>1.900641679017584</v>
       </c>
       <c r="E9" t="n">
-        <v>9.808017512166449</v>
+        <v>9.951805789543332</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507880315838247</v>
+        <v>0.7508592857769878</v>
       </c>
       <c r="G9" t="n">
-        <v>28.87085369336434</v>
+        <v>29.38474417220406</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53624945285593</v>
+        <v>34.53952714574142</v>
       </c>
       <c r="I9" t="n">
-        <v>4.627380827684421</v>
+        <v>4.712830772366273</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692425197398904</v>
+        <v>4.692870536106171</v>
       </c>
       <c r="K9" t="n">
-        <v>14.8485461016331</v>
+        <v>14.06672061924416</v>
       </c>
       <c r="L9" t="n">
-        <v>43.77675688066982</v>
+        <v>43.86503891386582</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84603287331689</v>
+        <v>99.84319230058563</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.50911787359493</v>
+        <v>83.69076725533509</v>
       </c>
       <c r="C10" t="n">
-        <v>39.2957541772785</v>
+        <v>40.40009863061654</v>
       </c>
       <c r="D10" t="n">
-        <v>1.746868337941788</v>
+        <v>1.800099010399396</v>
       </c>
       <c r="E10" t="n">
-        <v>9.826819097294347</v>
+        <v>10.0809472640151</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519594855854043</v>
+        <v>0.7520356457033442</v>
       </c>
       <c r="G10" t="n">
-        <v>27.0314203921751</v>
+        <v>27.83031093612811</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59013633692859</v>
+        <v>34.59363970235382</v>
       </c>
       <c r="I10" t="n">
-        <v>3.862167438760916</v>
+        <v>3.93351191108943</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699746784908776</v>
+        <v>4.700222785645899</v>
       </c>
       <c r="K10" t="n">
-        <v>17.49088212640508</v>
+        <v>16.3092327446649</v>
       </c>
       <c r="L10" t="n">
-        <v>43.08482533999185</v>
+        <v>43.15975665881949</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87146164367543</v>
+        <v>99.86908803410093</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.6330634559631</v>
+        <v>81.28453319277583</v>
       </c>
       <c r="C11" t="n">
-        <v>37.01742503963717</v>
+        <v>38.60347989244909</v>
       </c>
       <c r="D11" t="n">
-        <v>1.618908838037652</v>
+        <v>1.693301607346696</v>
       </c>
       <c r="E11" t="n">
-        <v>9.644132534536592</v>
+        <v>10.029914964785</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529738992632311</v>
+        <v>0.7530479070619256</v>
       </c>
       <c r="G11" t="n">
-        <v>25.05134727506966</v>
+        <v>26.17917679464098</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63679936610863</v>
+        <v>34.64020372484856</v>
       </c>
       <c r="I11" t="n">
-        <v>3.222814672552154</v>
+        <v>3.282338774955622</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706086870395193</v>
+        <v>4.706549419137033</v>
       </c>
       <c r="K11" t="n">
-        <v>20.3669365440369</v>
+        <v>18.71546680722419</v>
       </c>
       <c r="L11" t="n">
-        <v>42.50835598747146</v>
+        <v>42.57178908057424</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89271757114552</v>
+        <v>99.89073578024751</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>76.82051319334697</v>
+        <v>78.77182689374206</v>
       </c>
       <c r="C12" t="n">
-        <v>34.70242543325658</v>
+        <v>36.59861536021135</v>
       </c>
       <c r="D12" t="n">
-        <v>1.495266816272132</v>
+        <v>1.58287778029174</v>
       </c>
       <c r="E12" t="n">
-        <v>9.355710047612114</v>
+        <v>9.83225137793559</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538523996335837</v>
+        <v>0.7539205479629365</v>
       </c>
       <c r="G12" t="n">
-        <v>23.13808375320623</v>
+        <v>24.47197656624087</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67721038314485</v>
+        <v>34.68034520629507</v>
       </c>
       <c r="I12" t="n">
-        <v>2.688812295768158</v>
+        <v>2.738451990247503</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711577497709897</v>
+        <v>4.71200342476835</v>
       </c>
       <c r="K12" t="n">
-        <v>23.17948680665304</v>
+        <v>21.22817310625793</v>
       </c>
       <c r="L12" t="n">
-        <v>42.02856513029728</v>
+        <v>42.08203545644862</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91047737020691</v>
+        <v>99.90882392291792</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.23431430374434</v>
+        <v>76.27953479249818</v>
       </c>
       <c r="C13" t="n">
-        <v>32.53016027931147</v>
+        <v>34.52907472538829</v>
       </c>
       <c r="D13" t="n">
-        <v>1.382884587308023</v>
+        <v>1.47442022446382</v>
       </c>
       <c r="E13" t="n">
-        <v>9.026369815569881</v>
+        <v>9.539273371000522</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546116356132265</v>
+        <v>0.7546731293651284</v>
       </c>
       <c r="G13" t="n">
-        <v>21.39905671278383</v>
+        <v>22.79517574327181</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71213523820842</v>
+        <v>34.71496395079589</v>
       </c>
       <c r="I13" t="n">
-        <v>2.242933591678314</v>
+        <v>2.28432131506896</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716322722582665</v>
+        <v>4.71670705853205</v>
       </c>
       <c r="K13" t="n">
-        <v>25.76568569625564</v>
+        <v>23.72046520750181</v>
       </c>
       <c r="L13" t="n">
-        <v>41.62946479399487</v>
+        <v>41.67439195626967</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92531076956199</v>
+        <v>99.92393188915977</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>81.96029757717147</v>
+        <v>83.32599699107217</v>
       </c>
       <c r="C14" t="n">
-        <v>37.45085911494572</v>
+        <v>38.79538990929264</v>
       </c>
       <c r="D14" t="n">
-        <v>1.384447519979875</v>
+        <v>1.476274596286213</v>
       </c>
       <c r="E14" t="n">
-        <v>11.71488004835606</v>
+        <v>11.93185263018402</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554644957800721</v>
+        <v>0.7556222784360598</v>
       </c>
       <c r="G14" t="n">
-        <v>23.63839391732088</v>
+        <v>24.68043319540542</v>
       </c>
       <c r="H14" t="n">
-        <v>36.96651885050883</v>
+        <v>36.61521286805877</v>
       </c>
       <c r="I14" t="n">
-        <v>2.778939646600302</v>
+        <v>3.143962182476314</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721653098625449</v>
+        <v>4.72263924022537</v>
       </c>
       <c r="K14" t="n">
-        <v>18.03970242282852</v>
+        <v>16.67400300892783</v>
       </c>
       <c r="L14" t="n">
-        <v>44.41691171416964</v>
+        <v>44.42593998171441</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90747325194388</v>
+        <v>99.89533289993489</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>80.99085117165887</v>
+        <v>82.41991258239163</v>
       </c>
       <c r="C15" t="n">
-        <v>36.90970341572989</v>
+        <v>38.37475970586402</v>
       </c>
       <c r="D15" t="n">
-        <v>1.34920021799172</v>
+        <v>1.442684339555769</v>
       </c>
       <c r="E15" t="n">
-        <v>11.80295744998329</v>
+        <v>12.09748708490638</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561852195327253</v>
+        <v>0.7564237863968871</v>
       </c>
       <c r="G15" t="n">
-        <v>23.03657290432149</v>
+        <v>24.11886958837881</v>
       </c>
       <c r="H15" t="n">
-        <v>37.00178542933191</v>
+        <v>36.65405156490328</v>
       </c>
       <c r="I15" t="n">
-        <v>2.317992328418208</v>
+        <v>2.622747553269978</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726157622079532</v>
+        <v>4.727648664980541</v>
       </c>
       <c r="K15" t="n">
-        <v>19.00914882834112</v>
+        <v>17.58008741760834</v>
       </c>
       <c r="L15" t="n">
-        <v>44.00395498796787</v>
+        <v>43.95782059368107</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92280723203888</v>
+        <v>99.91266771715344</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.318052864324</v>
+        <v>79.81960652553835</v>
       </c>
       <c r="C16" t="n">
-        <v>34.5940608634413</v>
+        <v>36.17942923589426</v>
       </c>
       <c r="D16" t="n">
-        <v>1.250580224177097</v>
+        <v>1.344295914233785</v>
       </c>
       <c r="E16" t="n">
-        <v>11.26242677198757</v>
+        <v>11.63706393827451</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568074238146862</v>
+        <v>0.7571148311293384</v>
       </c>
       <c r="G16" t="n">
-        <v>21.35271112677452</v>
+        <v>22.47400692904088</v>
       </c>
       <c r="H16" t="n">
-        <v>37.03223123644324</v>
+        <v>36.68753754156403</v>
       </c>
       <c r="I16" t="n">
-        <v>1.933249682285093</v>
+        <v>2.187619676737443</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730046398841787</v>
+        <v>4.731967694558362</v>
       </c>
       <c r="K16" t="n">
-        <v>21.68194713567602</v>
+        <v>20.18039347446165</v>
       </c>
       <c r="L16" t="n">
-        <v>43.65960332509329</v>
+        <v>43.56732319094213</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93561132421061</v>
+        <v>99.92714590129805</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.28973604867103</v>
+        <v>81.5148982787088</v>
       </c>
       <c r="C17" t="n">
-        <v>36.02117867992275</v>
+        <v>37.39011867785688</v>
       </c>
       <c r="D17" t="n">
-        <v>1.251568542040342</v>
+        <v>1.345521709862298</v>
       </c>
       <c r="E17" t="n">
-        <v>12.12983649018979</v>
+        <v>12.42285394522863</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574055192279451</v>
+        <v>0.7578052059496845</v>
       </c>
       <c r="G17" t="n">
-        <v>21.9108352141072</v>
+        <v>22.89803197981983</v>
       </c>
       <c r="H17" t="n">
-        <v>37.60274665182661</v>
+        <v>37.12452319387877</v>
       </c>
       <c r="I17" t="n">
-        <v>1.903559136104483</v>
+        <v>2.229879706784046</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733784495174655</v>
+        <v>4.736282537185525</v>
       </c>
       <c r="K17" t="n">
-        <v>19.71026395132898</v>
+        <v>18.48510172129122</v>
       </c>
       <c r="L17" t="n">
-        <v>44.20515550324376</v>
+        <v>44.05051799270663</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93659813449548</v>
+        <v>99.92573839185472</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>77.81460282410914</v>
+        <v>79.09735437447804</v>
       </c>
       <c r="C18" t="n">
-        <v>33.83889575435128</v>
+        <v>35.31637445146084</v>
       </c>
       <c r="D18" t="n">
-        <v>1.164584263941075</v>
+        <v>1.257791755452671</v>
       </c>
       <c r="E18" t="n">
-        <v>11.5513732807751</v>
+        <v>11.92281420154782</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579205420156686</v>
+        <v>0.7583991079531929</v>
       </c>
       <c r="G18" t="n">
-        <v>20.38802753747444</v>
+        <v>21.405047298164</v>
       </c>
       <c r="H18" t="n">
-        <v>37.62831587586188</v>
+        <v>37.15361817571716</v>
       </c>
       <c r="I18" t="n">
-        <v>1.587377936443081</v>
+        <v>1.859689410935763</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737003387597927</v>
+        <v>4.739994424707453</v>
       </c>
       <c r="K18" t="n">
-        <v>22.18539717589083</v>
+        <v>20.90264562552195</v>
       </c>
       <c r="L18" t="n">
-        <v>43.92283042708834</v>
+        <v>43.719038820051</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94712335733045</v>
+        <v>99.93805889703378</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.88221739443188</v>
+        <v>78.16436026122415</v>
       </c>
       <c r="C19" t="n">
-        <v>33.1327771334513</v>
+        <v>34.66934844582707</v>
       </c>
       <c r="D19" t="n">
-        <v>1.131737406320554</v>
+        <v>1.224670518125624</v>
       </c>
       <c r="E19" t="n">
-        <v>11.44894423965234</v>
+        <v>11.86731357461025</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583609573470416</v>
+        <v>0.7589006577617115</v>
       </c>
       <c r="G19" t="n">
-        <v>19.81298744941724</v>
+        <v>20.84139147160469</v>
       </c>
       <c r="H19" t="n">
-        <v>37.65018107978075</v>
+        <v>37.17818886664543</v>
       </c>
       <c r="I19" t="n">
-        <v>1.340250278494954</v>
+        <v>1.550766061465735</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739755983419007</v>
+        <v>4.743129111010694</v>
       </c>
       <c r="K19" t="n">
-        <v>23.11778260556811</v>
+        <v>21.83563973877586</v>
       </c>
       <c r="L19" t="n">
-        <v>43.70479119654443</v>
+        <v>43.44335377620441</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95535093556384</v>
+        <v>99.94834196080734</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.35584675718542</v>
+        <v>75.56597842987114</v>
       </c>
       <c r="C20" t="n">
-        <v>30.81180528750388</v>
+        <v>32.30927856595286</v>
       </c>
       <c r="D20" t="n">
-        <v>1.043996329569265</v>
+        <v>1.131538810117895</v>
       </c>
       <c r="E20" t="n">
-        <v>10.74757224977081</v>
+        <v>11.18035486310366</v>
       </c>
       <c r="F20" t="n">
-        <v>0.75874085074737</v>
+        <v>0.7593335203471834</v>
       </c>
       <c r="G20" t="n">
-        <v>18.2769307256906</v>
+        <v>19.25647997395635</v>
       </c>
       <c r="H20" t="n">
-        <v>37.66904156458658</v>
+        <v>37.19939460258912</v>
       </c>
       <c r="I20" t="n">
-        <v>1.117434719649719</v>
+        <v>1.293042157587041</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74213031717106</v>
+        <v>4.745834502169894</v>
       </c>
       <c r="K20" t="n">
-        <v>25.64415324281459</v>
+        <v>24.43402157012885</v>
       </c>
       <c r="L20" t="n">
-        <v>43.50681229527889</v>
+        <v>43.21362302887758</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96277082559736</v>
+        <v>99.95692316495929</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.92806840597228</v>
+        <v>81.74897638383233</v>
       </c>
       <c r="C21" t="n">
-        <v>35.01123502194444</v>
+        <v>36.07310301079677</v>
       </c>
       <c r="D21" t="n">
-        <v>1.044636605867195</v>
+        <v>1.132441881141532</v>
       </c>
       <c r="E21" t="n">
-        <v>12.97152578110429</v>
+        <v>13.22657813044104</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592061816774176</v>
+        <v>0.7599395376515568</v>
       </c>
       <c r="G21" t="n">
-        <v>20.25733862068817</v>
+        <v>20.98293308306782</v>
       </c>
       <c r="H21" t="n">
-        <v>39.66134251762018</v>
+        <v>38.94016779169769</v>
       </c>
       <c r="I21" t="n">
-        <v>1.488980063531173</v>
+        <v>1.957293849510475</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745038635483857</v>
+        <v>4.749622110322227</v>
       </c>
       <c r="K21" t="n">
-        <v>19.07193159402771</v>
+        <v>18.25102361616765</v>
       </c>
       <c r="L21" t="n">
-        <v>45.86723113598621</v>
+        <v>45.61068227315344</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95039775195836</v>
+        <v>99.93480890011787</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_51_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_51_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.25870206488339</v>
+        <v>43.18800640950103</v>
       </c>
       <c r="M2" t="n">
-        <v>100.5276397246814</v>
+        <v>97.83739765149684</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0441503817095</v>
+        <v>81.60889630761591</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92741034658017</v>
+        <v>43.36445186317147</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228774775912142</v>
+        <v>2.1869896322446</v>
       </c>
       <c r="E3" t="n">
-        <v>5.706573525980716</v>
+        <v>4.168169813575139</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429249253040474</v>
+        <v>0.7377259995956512</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97249914922985</v>
+        <v>32.8959690516792</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17454656398618</v>
+        <v>33.93539598139995</v>
       </c>
       <c r="I3" t="n">
-        <v>6.575550658146275</v>
+        <v>3.073858331648546</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643280783150296</v>
+        <v>4.61078749747282</v>
       </c>
       <c r="K3" t="n">
-        <v>11.9558496182905</v>
+        <v>18.39110369238409</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88071616302837</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.763976127899</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.18285183697407</v>
+        <v>88.85502868545284</v>
       </c>
       <c r="C4" t="n">
-        <v>42.70274475643387</v>
+        <v>43.00938410432607</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187551620546124</v>
+        <v>2.192800570071494</v>
       </c>
       <c r="E4" t="n">
-        <v>6.516213723539072</v>
+        <v>6.59176859951539</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444846728721171</v>
+        <v>0.7396861734591795</v>
       </c>
       <c r="G4" t="n">
-        <v>33.34414781210228</v>
+        <v>33.59940678679892</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24629495211738</v>
+        <v>34.02556397912225</v>
       </c>
       <c r="I4" t="n">
-        <v>5.491129850346349</v>
+        <v>7.082763992365726</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65302920545073</v>
+        <v>4.623038584119872</v>
       </c>
       <c r="K4" t="n">
-        <v>12.81714816302593</v>
+        <v>11.14497131454718</v>
       </c>
       <c r="L4" t="n">
-        <v>44.2974528955917</v>
+        <v>45.61017809395725</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81734581505151</v>
+        <v>99.7645335128305</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.96436838222711</v>
+        <v>87.88056864703017</v>
       </c>
       <c r="C5" t="n">
-        <v>42.33657129797183</v>
+        <v>43.13291931258424</v>
       </c>
       <c r="D5" t="n">
-        <v>2.12793547466299</v>
+        <v>2.147192419449902</v>
       </c>
       <c r="E5" t="n">
-        <v>7.102643474630181</v>
+        <v>7.440590597940949</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458080017045735</v>
+        <v>0.7413458684494567</v>
       </c>
       <c r="G5" t="n">
-        <v>32.43543801908773</v>
+        <v>32.90057132203138</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30716807841038</v>
+        <v>34.101909948675</v>
       </c>
       <c r="I5" t="n">
-        <v>4.584075323077665</v>
+        <v>5.91554681267438</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661300010653583</v>
+        <v>4.633411677809105</v>
       </c>
       <c r="K5" t="n">
-        <v>14.03563161777291</v>
+        <v>12.11943135296984</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4752656995234</v>
+        <v>44.55090589021356</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84746861526813</v>
+        <v>99.80325655576763</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.6372952555857</v>
+        <v>86.67708442280698</v>
       </c>
       <c r="C6" t="n">
-        <v>41.72142897164933</v>
+        <v>42.84781970763105</v>
       </c>
       <c r="D6" t="n">
-        <v>2.063264341688932</v>
+        <v>2.09033593248187</v>
       </c>
       <c r="E6" t="n">
-        <v>7.524419987362557</v>
+        <v>8.066732070287792</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469317482965094</v>
+        <v>0.7427539670938235</v>
       </c>
       <c r="G6" t="n">
-        <v>31.44967667896231</v>
+        <v>32.02938209480266</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35886042163943</v>
+        <v>34.16668248631587</v>
       </c>
       <c r="I6" t="n">
-        <v>3.825818650782797</v>
+        <v>4.938985577488562</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668323426853182</v>
+        <v>4.642212294336397</v>
       </c>
       <c r="K6" t="n">
-        <v>15.36270474441428</v>
+        <v>13.32291557719302</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78853085829535</v>
+        <v>43.66494397037943</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87266457435896</v>
+        <v>99.8356792552035</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.06215224956689</v>
+        <v>85.19301579061977</v>
       </c>
       <c r="C7" t="n">
-        <v>40.7405134517891</v>
+        <v>42.13110565157459</v>
       </c>
       <c r="D7" t="n">
-        <v>1.986611508938463</v>
+        <v>2.020053501133571</v>
       </c>
       <c r="E7" t="n">
-        <v>7.776922858419468</v>
+        <v>8.482584622150812</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478886242187196</v>
+        <v>0.7439520205393787</v>
       </c>
       <c r="G7" t="n">
-        <v>30.28128213163276</v>
+        <v>30.95247248748722</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40287671406109</v>
+        <v>34.22179294481141</v>
       </c>
       <c r="I7" t="n">
-        <v>3.19226651092939</v>
+        <v>4.122460086126256</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674303901366995</v>
+        <v>4.649700128371117</v>
       </c>
       <c r="K7" t="n">
-        <v>16.9378477504331</v>
+        <v>14.80698420938022</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21536605747828</v>
+        <v>42.92471609522607</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89372725970048</v>
+        <v>99.86280595618088</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.9272910022987</v>
+        <v>83.51534424774411</v>
       </c>
       <c r="C8" t="n">
-        <v>43.02932077859809</v>
+        <v>41.09395498928618</v>
       </c>
       <c r="D8" t="n">
-        <v>1.99086296684368</v>
+        <v>1.940964123378811</v>
       </c>
       <c r="E8" t="n">
-        <v>9.601449390557452</v>
+        <v>8.723823502985724</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494891470131113</v>
+        <v>0.7449734973362654</v>
       </c>
       <c r="G8" t="n">
-        <v>30.77960438753249</v>
+        <v>29.74061756006427</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47650076260311</v>
+        <v>34.2687808774682</v>
       </c>
       <c r="I8" t="n">
-        <v>5.645077178916916</v>
+        <v>3.440100328159176</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684307168831944</v>
+        <v>4.656084358351659</v>
       </c>
       <c r="K8" t="n">
-        <v>12.0727089977013</v>
+        <v>16.48465575225588</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71020281698214</v>
+        <v>42.30687647828774</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81223259328154</v>
+        <v>99.8854872198298</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.93327938075582</v>
+        <v>81.54380053294435</v>
       </c>
       <c r="C9" t="n">
-        <v>41.91143276747566</v>
+        <v>39.65662668120963</v>
       </c>
       <c r="D9" t="n">
-        <v>1.900641679017584</v>
+        <v>1.848422708149881</v>
       </c>
       <c r="E9" t="n">
-        <v>9.951805789543332</v>
+        <v>8.786240748439916</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508592857769878</v>
+        <v>0.7458475301043058</v>
       </c>
       <c r="G9" t="n">
-        <v>29.38474417220406</v>
+        <v>28.32264243850475</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53952714574142</v>
+        <v>34.30898638479807</v>
       </c>
       <c r="I9" t="n">
-        <v>4.712830772366273</v>
+        <v>2.870113659795504</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692870536106171</v>
+        <v>4.661547063151913</v>
       </c>
       <c r="K9" t="n">
-        <v>14.06672061924416</v>
+        <v>18.45619946705565</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86503891386582</v>
+        <v>41.79161550928585</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84319230058563</v>
+        <v>99.90444165755113</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.69076725533509</v>
+        <v>86.13546439631524</v>
       </c>
       <c r="C10" t="n">
-        <v>40.40009863061654</v>
+        <v>42.86477506101996</v>
       </c>
       <c r="D10" t="n">
-        <v>1.800099010399396</v>
+        <v>1.850472548831039</v>
       </c>
       <c r="E10" t="n">
-        <v>10.0809472640151</v>
+        <v>10.61735186266782</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520356457033442</v>
+        <v>0.7466746507636706</v>
       </c>
       <c r="G10" t="n">
-        <v>27.83031093612811</v>
+        <v>29.69781164053536</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59363970235382</v>
+        <v>35.69079424761681</v>
       </c>
       <c r="I10" t="n">
-        <v>3.93351191108943</v>
+        <v>2.865642878627602</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700222785645899</v>
+        <v>4.666716567272942</v>
       </c>
       <c r="K10" t="n">
-        <v>16.3092327446649</v>
+        <v>13.86453560368473</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15975665881949</v>
+        <v>43.17527371882392</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86908803410093</v>
+        <v>99.90458438352861</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.28453319277583</v>
+        <v>85.80179780407292</v>
       </c>
       <c r="C11" t="n">
-        <v>38.60347989244909</v>
+        <v>42.86911133135114</v>
       </c>
       <c r="D11" t="n">
-        <v>1.693301607346696</v>
+        <v>1.829196020511069</v>
       </c>
       <c r="E11" t="n">
-        <v>10.029914964785</v>
+        <v>10.94118232710732</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530479070619256</v>
+        <v>0.7473881501894485</v>
       </c>
       <c r="G11" t="n">
-        <v>26.17917679464098</v>
+        <v>29.39230924325943</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64020372484856</v>
+        <v>35.76085902762076</v>
       </c>
       <c r="I11" t="n">
-        <v>3.282338774955622</v>
+        <v>2.459687096700827</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706549419137033</v>
+        <v>4.671175938684055</v>
       </c>
       <c r="K11" t="n">
-        <v>18.71546680722419</v>
+        <v>14.19820219592709</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57178908057424</v>
+        <v>42.85077517475911</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89073578024751</v>
+        <v>99.91808870203735</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.77182689374206</v>
+        <v>83.9749322235793</v>
       </c>
       <c r="C12" t="n">
-        <v>36.59861536021135</v>
+        <v>41.42483336844879</v>
       </c>
       <c r="D12" t="n">
-        <v>1.58287778029174</v>
+        <v>1.751363816245991</v>
       </c>
       <c r="E12" t="n">
-        <v>9.83225137793559</v>
+        <v>10.8175369255101</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539205479629365</v>
+        <v>0.7479967438264775</v>
       </c>
       <c r="G12" t="n">
-        <v>24.47197656624087</v>
+        <v>28.14166787339435</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68034520629507</v>
+        <v>35.78997887820093</v>
       </c>
       <c r="I12" t="n">
-        <v>2.738451990247503</v>
+        <v>2.051408337485969</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71200342476835</v>
+        <v>4.674979648915486</v>
       </c>
       <c r="K12" t="n">
-        <v>21.22817310625793</v>
+        <v>16.02506777642069</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08203545644862</v>
+        <v>42.48177421355551</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90882392291792</v>
+        <v>99.931675358425</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.27953479249818</v>
+        <v>85.09049213991499</v>
       </c>
       <c r="C13" t="n">
-        <v>34.52907472538829</v>
+        <v>42.37666954671261</v>
       </c>
       <c r="D13" t="n">
-        <v>1.47442022446382</v>
+        <v>1.752657352282836</v>
       </c>
       <c r="E13" t="n">
-        <v>9.539273371000522</v>
+        <v>11.44203478028785</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546731293651284</v>
+        <v>0.7485492051338354</v>
       </c>
       <c r="G13" t="n">
-        <v>22.79517574327181</v>
+        <v>28.46472710228866</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71496395079589</v>
+        <v>36.11868705668181</v>
       </c>
       <c r="I13" t="n">
-        <v>2.28432131506896</v>
+        <v>1.885404111153507</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71670705853205</v>
+        <v>4.678432532086473</v>
       </c>
       <c r="K13" t="n">
-        <v>23.72046520750181</v>
+        <v>14.90950786008504</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67439195626967</v>
+        <v>42.65102217312452</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92393188915977</v>
+        <v>99.93719957992215</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.32599699107217</v>
+        <v>83.2206358274524</v>
       </c>
       <c r="C14" t="n">
-        <v>38.79538990929264</v>
+        <v>40.79997380963528</v>
       </c>
       <c r="D14" t="n">
-        <v>1.476274596286213</v>
+        <v>1.675044588729554</v>
       </c>
       <c r="E14" t="n">
-        <v>11.93185263018402</v>
+        <v>11.19737479200626</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556222784360598</v>
+        <v>0.7490205780969501</v>
       </c>
       <c r="G14" t="n">
-        <v>24.68043319540542</v>
+        <v>27.20422622268369</v>
       </c>
       <c r="H14" t="n">
-        <v>36.61521286805877</v>
+        <v>36.14143155019667</v>
       </c>
       <c r="I14" t="n">
-        <v>3.143962182476314</v>
+        <v>1.572159482633335</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72263924022537</v>
+        <v>4.681378613105941</v>
       </c>
       <c r="K14" t="n">
-        <v>16.67400300892783</v>
+        <v>16.7793641725476</v>
       </c>
       <c r="L14" t="n">
-        <v>44.42593998171441</v>
+        <v>42.36828968139621</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89533289993489</v>
+        <v>99.94762766357908</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.41991258239163</v>
+        <v>82.39911916601571</v>
       </c>
       <c r="C15" t="n">
-        <v>38.37475970586402</v>
+        <v>40.19563838702134</v>
       </c>
       <c r="D15" t="n">
-        <v>1.442684339555769</v>
+        <v>1.640291019929492</v>
       </c>
       <c r="E15" t="n">
-        <v>12.09748708490638</v>
+        <v>11.18786261350472</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564237863968871</v>
+        <v>0.7494256521015671</v>
       </c>
       <c r="G15" t="n">
-        <v>24.11886958837881</v>
+        <v>26.63979709999414</v>
       </c>
       <c r="H15" t="n">
-        <v>36.65405156490328</v>
+        <v>36.16097701375099</v>
       </c>
       <c r="I15" t="n">
-        <v>2.622747553269978</v>
+        <v>1.336855441099999</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727648664980541</v>
+        <v>4.683910325634796</v>
       </c>
       <c r="K15" t="n">
-        <v>17.58008741760834</v>
+        <v>17.60088083398428</v>
       </c>
       <c r="L15" t="n">
-        <v>43.95782059368107</v>
+        <v>42.15894301719786</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91266771715344</v>
+        <v>99.95546223820349</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.81960652553835</v>
+        <v>80.18821351857486</v>
       </c>
       <c r="C16" t="n">
-        <v>36.17942923589426</v>
+        <v>38.19214510490851</v>
       </c>
       <c r="D16" t="n">
-        <v>1.344295914233785</v>
+        <v>1.549123007166484</v>
       </c>
       <c r="E16" t="n">
-        <v>11.63706393827451</v>
+        <v>10.75179725050623</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571148311293384</v>
+        <v>0.7497728692214968</v>
       </c>
       <c r="G16" t="n">
-        <v>22.47400692904088</v>
+        <v>25.15914681750915</v>
       </c>
       <c r="H16" t="n">
-        <v>36.68753754156403</v>
+        <v>36.17773079080325</v>
       </c>
       <c r="I16" t="n">
-        <v>2.187619676737443</v>
+        <v>1.114562350733884</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731967694558362</v>
+        <v>4.686080432634357</v>
       </c>
       <c r="K16" t="n">
-        <v>20.18039347446165</v>
+        <v>19.81178648142514</v>
       </c>
       <c r="L16" t="n">
-        <v>43.56732319094213</v>
+        <v>41.95893354030245</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92714590129805</v>
+        <v>99.9628651266361</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.5148982787088</v>
+        <v>84.7916579562193</v>
       </c>
       <c r="C17" t="n">
-        <v>37.39011867785688</v>
+        <v>41.26088490113104</v>
       </c>
       <c r="D17" t="n">
-        <v>1.345521709862298</v>
+        <v>1.549855065925929</v>
       </c>
       <c r="E17" t="n">
-        <v>12.42285394522863</v>
+        <v>12.38329511528372</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7578052059496845</v>
+        <v>0.7501271844010975</v>
       </c>
       <c r="G17" t="n">
-        <v>22.89803197981983</v>
+        <v>26.59710591755618</v>
       </c>
       <c r="H17" t="n">
-        <v>37.12452319387877</v>
+        <v>37.62089686981646</v>
       </c>
       <c r="I17" t="n">
-        <v>2.229879706784046</v>
+        <v>1.202082900729037</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736282537185525</v>
+        <v>4.688294902506862</v>
       </c>
       <c r="K17" t="n">
-        <v>18.48510172129122</v>
+        <v>15.20834204378072</v>
       </c>
       <c r="L17" t="n">
-        <v>44.05051799270663</v>
+        <v>43.49072255146413</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92573839185472</v>
+        <v>99.95994949637588</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.09735437447804</v>
+        <v>86.47270455020109</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31637445146084</v>
+        <v>41.97982740177716</v>
       </c>
       <c r="D18" t="n">
-        <v>1.257791755452671</v>
+        <v>1.551118621480341</v>
       </c>
       <c r="E18" t="n">
-        <v>11.92281420154782</v>
+        <v>12.97756527846263</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583991079531929</v>
+        <v>0.7507387431146856</v>
       </c>
       <c r="G18" t="n">
-        <v>21.405047298164</v>
+        <v>26.73462979385534</v>
       </c>
       <c r="H18" t="n">
-        <v>37.15361817571716</v>
+        <v>37.65156818499097</v>
       </c>
       <c r="I18" t="n">
-        <v>1.859689410935763</v>
+        <v>2.114966783830328</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739994424707453</v>
+        <v>4.692117144466788</v>
       </c>
       <c r="K18" t="n">
-        <v>20.90264562552195</v>
+        <v>13.52729544979891</v>
       </c>
       <c r="L18" t="n">
-        <v>43.719038820051</v>
+        <v>44.42243568467876</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93805889703378</v>
+        <v>99.92955853625483</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.16436026122415</v>
+        <v>84.01003952148319</v>
       </c>
       <c r="C19" t="n">
-        <v>34.66934844582707</v>
+        <v>39.84513279483819</v>
       </c>
       <c r="D19" t="n">
-        <v>1.224670518125624</v>
+        <v>1.459565902545316</v>
       </c>
       <c r="E19" t="n">
-        <v>11.86731357461025</v>
+        <v>12.50553265334435</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7589006577617115</v>
+        <v>0.7512641097676519</v>
       </c>
       <c r="G19" t="n">
-        <v>20.84139147160469</v>
+        <v>25.15665373615522</v>
       </c>
       <c r="H19" t="n">
-        <v>37.17818886664543</v>
+        <v>37.67791673638478</v>
       </c>
       <c r="I19" t="n">
-        <v>1.550766061465735</v>
+        <v>1.76370569723805</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743129111010694</v>
+        <v>4.695400686047827</v>
       </c>
       <c r="K19" t="n">
-        <v>21.83563973877586</v>
+        <v>15.98996047851682</v>
       </c>
       <c r="L19" t="n">
-        <v>43.44335377620441</v>
+        <v>44.10615764931637</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94834196080734</v>
+        <v>99.94125092267137</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.56597842987114</v>
+        <v>81.42140644483338</v>
       </c>
       <c r="C20" t="n">
-        <v>32.30927856595286</v>
+        <v>37.52934244977911</v>
       </c>
       <c r="D20" t="n">
-        <v>1.131538810117895</v>
+        <v>1.363809027630701</v>
       </c>
       <c r="E20" t="n">
-        <v>11.18035486310366</v>
+        <v>11.93019619299492</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7593335203471834</v>
+        <v>0.7517164227524491</v>
       </c>
       <c r="G20" t="n">
-        <v>19.25647997395635</v>
+        <v>23.50621606774819</v>
       </c>
       <c r="H20" t="n">
-        <v>37.19939460258912</v>
+        <v>37.70060144973445</v>
       </c>
       <c r="I20" t="n">
-        <v>1.293042157587041</v>
+        <v>1.470639641769858</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745834502169894</v>
+        <v>4.698227642202809</v>
       </c>
       <c r="K20" t="n">
-        <v>24.43402157012885</v>
+        <v>18.57859355516664</v>
       </c>
       <c r="L20" t="n">
-        <v>43.21362302887758</v>
+        <v>43.84307217013098</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95692316495929</v>
+        <v>99.95100817507672</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.74897638383233</v>
+        <v>78.72832522992874</v>
       </c>
       <c r="C21" t="n">
-        <v>36.07310301079677</v>
+        <v>35.06311200202299</v>
       </c>
       <c r="D21" t="n">
-        <v>1.132441881141532</v>
+        <v>1.264660178430088</v>
       </c>
       <c r="E21" t="n">
-        <v>13.22657813044104</v>
+        <v>11.26723306314866</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7599395376515568</v>
+        <v>0.7521066811000412</v>
       </c>
       <c r="G21" t="n">
-        <v>20.98293308306782</v>
+        <v>21.79731531627927</v>
       </c>
       <c r="H21" t="n">
-        <v>38.94016779169769</v>
+        <v>37.72017395604092</v>
       </c>
       <c r="I21" t="n">
-        <v>1.957293849510475</v>
+        <v>1.226169278054482</v>
       </c>
       <c r="J21" t="n">
-        <v>4.749622110322227</v>
+        <v>4.70066675687526</v>
       </c>
       <c r="K21" t="n">
-        <v>18.25102361616765</v>
+        <v>21.27167477007128</v>
       </c>
       <c r="L21" t="n">
-        <v>45.61068227315344</v>
+        <v>43.62436212674547</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93480890011787</v>
+        <v>99.95914889883973</v>
       </c>
     </row>
   </sheetData>
